--- a/outputs/evaluation/architecture/validation/CF_M04/run_1/CF_M04_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/run_1/CF_M04_arch_eval_gt_report.xlsx
@@ -507,7 +507,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -557,7 +557,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,33 +607,29 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Finally, the system integrates several external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT) and authentication services.</t>
+          <t>The back-end integrates several external services, such as artificial intelligence services (Gemini or ChatGPT) and authentication services.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.8413</v>
+        <v>0.8619</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M04_AU18</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Authentication Service</t>
-        </is>
-      </c>
+          <t>CF_M04_AU19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -644,262 +640,274 @@
       <c r="E5" t="n">
         <v>68</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CF_M04_AU04, CF_M04_AU18</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>backend, authentication service</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Authentication Service</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Finally, the system integrates several external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT) and authentication services.</t>
+          <t>Service responsible for managing user authentication, including delegated login and OTP generation.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.7315</v>
+        <v>0.7536</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M04_AU19</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>CF_M04_AU20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The back-end, in turn, delegates the code generation to a specialized authentication service, responsible for creating and send the OTP to the user.</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>68</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CF_M04_AU04, CF_M04_AU18</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>backend, authentication service</t>
-        </is>
-      </c>
+          <t>Users: Application customers who use the new features and provide feedback.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Finally, the system integrates several external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT) and authentication services.</t>
+          <t>AI service integrated for generating review responses.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.7104</v>
+        <v>0.718</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M04_AU20</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
+          <t>CF_M04_AU21</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Users: Application customers who use the new features and provide feedback.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>This confirmation allows the front-end to inform the user that they can enter the received code.</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>68</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CF_M04_AU01, CF_M04_AU21</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ChatGPT</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AI service provider used for generating review responses.</t>
+          <t>The frontend is the mobile application developed with Flutter that acts as the presentation layer, managing the graphical interface, navigation, and user interaction.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.718</v>
+        <v>0.7078</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M04_AU21</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>CF_M04_AU24</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Presentation Layer</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>This confirmation allows the front-end to inform the user that they can enter the received code.</t>
+          <t>Presentation: manages the application state and communication with the interface user via Bloc/Cubit.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M04_AU01, CF_M04_AU21</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>frontend</t>
-        </is>
-      </c>
+          <t>CF_M04_P08</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Presentation Layer (Frontend)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>The frontend is the mobile application developed with Flutter that manages the graphical interface, navigation, and user interaction.</t>
+          <t>Manages the application state and communication with the user interface using Bloc/Cubit.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.7078</v>
+        <v>0.9486</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M04_AU24</t>
+          <t>CF_M04_AU26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Google Login</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Presentation: manages the application state and communication with the interface user via Bloc/Cubit.</t>
+          <t>Authentication services, such as Google login.</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M04_P08</t>
+          <t>CF_M04_AU18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Presentation Layer (Frontend)</t>
+          <t>Authentication Service</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Manages the state of the application and the communication with the user interface using Bloc/Cubit.</t>
+          <t>Service responsible for managing user authentication, including delegated login and OTP generation.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.9486</v>
+        <v>0.6734</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M04_AU26</t>
+          <t>CF_M04_AU27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Google Login</t>
+          <t>Firebase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Authentication services, such as Google login.</t>
+          <t>Firebase for complementary functionalities (notifications, services associated).</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CF_M04_AU18</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Firebase</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Used for complementary functionalities like notifications.</t>
+          <t>The backend is the software responsible for processing user requests, business logic, data persistence, and integration with external services.</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.6531</v>
+        <v>0.6827</v>
       </c>
     </row>
     <row r="11">
@@ -935,7 +943,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -945,7 +953,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Handles data access, including calls to the backend, data transformation, and concrete implementation of repositories.</t>
+          <t>Responsible for data access, including backend calls, data transformation, and concrete implementation of repositories.</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1135,21 +1143,17 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Repository Pattern</t>
-        </is>
-      </c>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Isolates data access and simplifies the use of the ORM in use cases.</t>
+          <t>The persistence of data is carried out through a MySQL relational database, managed through the Django ORM.</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.6841</v>
+        <v>0.7453</v>
       </c>
     </row>
   </sheetData>
